--- a/output/Test Results 0: Aiming for 70%.xlsx
+++ b/output/Test Results 0: Aiming for 70%.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\neomi\forks\nimendoza\B2023-R3X-07\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\lunar-bloom\forks\nimendoza\B2023-R3X-07\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A52D79F-0752-48D1-A6A4-02603D3EC3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCA7881-D959-40FA-93AA-2C51EE62B109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="997" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="997" firstSheet="12" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -8981,6 +8981,9 @@
       <c r="B9" t="s">
         <v>274</v>
       </c>
+      <c r="C9" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -8989,6 +8992,9 @@
       <c r="B10" t="s">
         <v>164</v>
       </c>
+      <c r="C10" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -8997,6 +9003,9 @@
       <c r="B11" t="s">
         <v>176</v>
       </c>
+      <c r="C11" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -9005,6 +9014,9 @@
       <c r="B12" t="s">
         <v>130</v>
       </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -9013,6 +9025,9 @@
       <c r="B13" t="s">
         <v>269</v>
       </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -9021,6 +9036,9 @@
       <c r="B14" t="s">
         <v>275</v>
       </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -9029,6 +9047,9 @@
       <c r="B15" t="s">
         <v>152</v>
       </c>
+      <c r="C15" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -9037,131 +9058,110 @@
       <c r="B16" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>183</v>
       </c>
       <c r="B17" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>171</v>
       </c>
       <c r="B18" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
       <c r="B20" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>184</v>
-      </c>
+      <c r="C20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>264</v>
-      </c>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>270</v>
-      </c>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
-      </c>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>84</v>
-      </c>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>271</v>
-      </c>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>179</v>
-      </c>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>97</v>
-      </c>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>85</v>
-      </c>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>180</v>
-      </c>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>174</v>
       </c>
